--- a/testakten/kuendigungsschutzklage-weber-techlogix/annahmeverzug_berechnung.xlsx
+++ b/testakten/kuendigungsschutzklage-weber-techlogix/annahmeverzug_berechnung.xlsx
@@ -82,7 +82,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -104,11 +104,55 @@
         <color rgb="00888888"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00888888"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00888888"/>
+      </right>
+      <top style="thin">
+        <color rgb="00888888"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00888888"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00888888"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00888888"/>
+      </right>
+      <top style="thin">
+        <color rgb="00888888"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00888888"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -148,6 +192,8 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -537,6 +583,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -593,7 +640,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Betriebsjahre (aufgerundet für § 1a KSchG)</t>
+          <t>Betriebsjahre (aufgerundet für Paragraf 1a KSchG)</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
@@ -612,10 +659,11 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2. ANNAHMEVERZUGSLOHN (§§ 615, 611a BGB)</t>
+          <t>2. ANNAHMEVERZUGSLOHN (Paragrafen 615, 611a BGB)</t>
         </is>
       </c>
     </row>
@@ -709,6 +757,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
@@ -822,7 +871,7 @@
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>§ 1a KSchG Regelabfindung (0,5 × n × aufger. Jahre)</t>
+          <t>Paragraf 1a KSchG Regelabfindung (0,5 × n × aufger. Jahre)</t>
         </is>
       </c>
       <c r="B24" s="9" t="n">
@@ -838,6 +887,7 @@
         <v>21825</v>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="14" t="inlineStr">
         <is>
@@ -859,6 +909,8 @@
           <t>brutto, steuerpflichtig nach Fünftelregelung</t>
         </is>
       </c>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="18" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -873,6 +925,8 @@
         <f> 24.250 / 4.850</f>
         <v/>
       </c>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="18" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -887,6 +941,8 @@
         <f> 24.250 / (4.850 × 8,5)</f>
         <v/>
       </c>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="18" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -902,6 +958,8 @@
           <t>Unterschreitung um EUR 750,00</t>
         </is>
       </c>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="18" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -919,6 +977,8 @@
           <t>mit positiver Schlussformel</t>
         </is>
       </c>
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="18" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -936,6 +996,8 @@
           <t>unwiderruflich, Urlaub angerechnet</t>
         </is>
       </c>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
